--- a/despiece-cocina.xlsx
+++ b/despiece-cocina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e4bb88fb3ffb2f3/Desktop/proyecto_terraza/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="11_94BACD76368ECBCEC412C0D0708AC5833D8EAE39" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01178C22-1E2B-4766-A906-4C26A5CFEDA8}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="11_94BACD76368ECBCEC412C0D0708AC5833D8EAE39" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4EBE661-2EB4-46AA-93E2-FC72075785C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="415">
   <si>
     <t>Diseño final 260 · condimentero, puertas y basurero · tablero RH 15 mm / fondos 6 mm</t>
   </si>
@@ -491,15 +491,6 @@
     <t>¿El proveedor pide medida terminada y descuenta el canto? (SÍ/NO)</t>
   </si>
   <si>
-    <t>Confirmar con el manual del horno antes de cortar (nicho, apoyos y ventilación).</t>
-  </si>
-  <si>
-    <t>Confirmar con el manual del horno antes de cortar.</t>
-  </si>
-  <si>
-    <t>Ajustar con la estufa real antes de cortar.</t>
-  </si>
-  <si>
     <t>Supuestos por confirmar en la sucursal: Q2 cambia la medida que se pide; Q3 y Q4 marcan qué piezas pueden rechazar.</t>
   </si>
   <si>
@@ -542,9 +533,6 @@
     <t>Angosta con canto rígido de 2 mm: preguntar si la canteadora la acepta; si no, canteadora manual en taller.</t>
   </si>
   <si>
-    <t>NO CORTAR hasta confirmar el riel HRE126-55 y la bandeja.</t>
-  </si>
-  <si>
     <t>Metros netos de canto</t>
   </si>
   <si>
@@ -1142,9 +1130,6 @@
     <t>Confirmar el descuento real del riel HRE126-55 (27 mm es un supuesto), la bandeja HSO688-00, las holguras y la fijación rígida del frente. Riel montado vertical en los largueros, no acostado.</t>
   </si>
   <si>
-    <t>No cortar P072–P074</t>
-  </si>
-  <si>
     <t>Ficha HRE126 y piezas reales</t>
   </si>
   <si>
@@ -1154,9 +1139,6 @@
     <t>Nicho, tapetas, apoyos y ventilación según el manual del horno H60EEVAL005 (Haceb publica ruteo 540 × 540 × 605); panel bajo la estufa según la estufa real. No ensanchar el hueco por el frente.</t>
   </si>
   <si>
-    <t>No cortar P007, P009 y P011</t>
-  </si>
-  <si>
     <t>Manuales del horno y la estufa</t>
   </si>
   <si>
@@ -1278,6 +1260,30 @@
   </si>
   <si>
     <t>Previsión de 1 lámina: los 9 fondos de la cocina caben en una (60 % de ocupación). Confirmar formato del suministro.</t>
+  </si>
+  <si>
+    <t>Ranura de ventilación o paso de cable en obra, si el manual del horno lo pide.</t>
+  </si>
+  <si>
+    <t>Su altura se fija en el armado según el manual del horno; si pide más ventilación atrás, recortar el borde trasero (sin canto).</t>
+  </si>
+  <si>
+    <t>Pedida 15 mm más alta (160 en vez de 145): en el armado, recortar el borde superior —oculto bajo el mesón y sin canto— según el horno instalado.</t>
+  </si>
+  <si>
+    <t>NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</t>
+  </si>
+  <si>
+    <t>Corte de P072–P074 en el armado, de un sobrante</t>
+  </si>
+  <si>
+    <t>Altura de P009 y recorte de P011 en el armado</t>
+  </si>
+  <si>
+    <t>Piezas que se ajustan en el armado</t>
+  </si>
+  <si>
+    <t>P011 se pide 15 mm más alta (160) y se recorta arriba, oculta bajo el mesón, según el horno instalado. P007 y P009 se cortan con la medida del módulo; ranuras y altura de la repisa se resuelven en obra. P072–P074 no se piden: se cortan en el armado de un sobrante, con el riel y la bandeja en mano.</t>
   </si>
 </sst>
 </file>
@@ -1648,6 +1654,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1971,7 +1981,7 @@
     </row>
     <row r="3" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -5308,21 +5318,21 @@
         <v>149</v>
       </c>
       <c r="Q2" s="31" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="S2" s="28" t="s">
         <v>33</v>
       </c>
       <c r="T2" s="28" t="s">
-        <v>150</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q3" s="33">
         <v>100</v>
@@ -5331,15 +5341,15 @@
         <v>37</v>
       </c>
       <c r="T3" s="28" t="s">
-        <v>151</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="Q4" s="33">
         <v>250</v>
@@ -5348,26 +5358,26 @@
         <v>41</v>
       </c>
       <c r="T4" s="28" t="s">
-        <v>152</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P5" s="30" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="S5" s="28" t="s">
         <v>72</v>
       </c>
       <c r="T5" s="28" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C6" s="39" t="s">
         <v>4</v>
@@ -5379,37 +5389,37 @@
         <v>8</v>
       </c>
       <c r="F6" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="J6" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="K6" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="L6" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="M6" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="N6" s="39" t="s">
         <v>161</v>
-      </c>
-      <c r="L6" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="M6" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="N6" s="39" t="s">
-        <v>164</v>
       </c>
       <c r="S6" s="28" t="s">
         <v>109</v>
       </c>
       <c r="T6" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -5473,7 +5483,7 @@
         <v>111</v>
       </c>
       <c r="T7" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -5537,7 +5547,7 @@
         <v>116</v>
       </c>
       <c r="T8" s="28" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
@@ -5601,7 +5611,7 @@
         <v>85</v>
       </c>
       <c r="T9" s="28" t="s">
-        <v>167</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -5665,7 +5675,7 @@
         <v>87</v>
       </c>
       <c r="T10" s="28" t="s">
-        <v>167</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -5729,7 +5739,7 @@
         <v>89</v>
       </c>
       <c r="T11" s="28" t="s">
-        <v>167</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -5793,7 +5803,7 @@
         <v>15</v>
       </c>
       <c r="T12" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -5851,13 +5861,13 @@
       </c>
       <c r="N13" s="43" t="str">
         <f>IF(LEN(TRIM(IF($L13="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L11,2)&amp;" × "&amp;ROUND(Despiece!M11,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A11,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L13="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L11,2)&amp;" × "&amp;ROUND(Despiece!M11,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A11,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>Confirmar con el manual del horno antes de cortar (nicho, apoyos y ventilación).</v>
+        <v>Ranura de ventilación o paso de cable en obra, si el manual del horno lo pide.</v>
       </c>
       <c r="S13" s="28" t="s">
         <v>24</v>
       </c>
       <c r="T13" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="88.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5921,7 +5931,7 @@
         <v>43</v>
       </c>
       <c r="T14" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -5979,13 +5989,13 @@
       </c>
       <c r="N15" s="43" t="str">
         <f>IF(LEN(TRIM(IF($L15="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L13,2)&amp;" × "&amp;ROUND(Despiece!M13,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A13,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L15="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L13,2)&amp;" × "&amp;ROUND(Despiece!M13,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A13,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>Confirmar con el manual del horno antes de cortar.</v>
+        <v>Su altura se fija en el armado según el manual del horno; si pide más ventilación atrás, recortar el borde trasero (sin canto).</v>
       </c>
       <c r="S15" s="28" t="s">
         <v>46</v>
       </c>
       <c r="T15" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -6049,7 +6059,7 @@
         <v>62</v>
       </c>
       <c r="T16" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -6074,8 +6084,8 @@
         <v>1</v>
       </c>
       <c r="F17" s="45">
-        <f>IF($Q$2="NO",ROUND(Despiece!L15,2),Despiece!E15)</f>
-        <v>145</v>
+        <f>IF($Q$2="NO",ROUND(Despiece!L15,2),Despiece!E15)+15</f>
+        <v>160</v>
       </c>
       <c r="G17" s="45">
         <f>IF($Q$2="NO",ROUND(Despiece!M15,2),Despiece!F15)</f>
@@ -6107,13 +6117,13 @@
       </c>
       <c r="N17" s="43" t="str">
         <f>IF(LEN(TRIM(IF($L17="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L15,2)&amp;" × "&amp;ROUND(Despiece!M15,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A15,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L17="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L15,2)&amp;" × "&amp;ROUND(Despiece!M15,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A15,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>Ajustar con la estufa real antes de cortar.</v>
+        <v>Pedida 15 mm más alta (160 en vez de 145): en el armado, recortar el borde superior —oculto bajo el mesón y sin canto— según el horno instalado.</v>
       </c>
       <c r="S17" s="28" t="s">
         <v>65</v>
       </c>
       <c r="T17" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -6177,7 +6187,7 @@
         <v>74</v>
       </c>
       <c r="T18" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -6241,7 +6251,7 @@
         <v>77</v>
       </c>
       <c r="T19" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="88.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6305,7 +6315,7 @@
         <v>79</v>
       </c>
       <c r="T20" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -7639,7 +7649,7 @@
       </c>
       <c r="N43" s="43" t="str">
         <f>IF(LEN(TRIM(IF($L43="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L41,2)&amp;" × "&amp;ROUND(Despiece!M41,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A41,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L43="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L41,2)&amp;" × "&amp;ROUND(Despiece!M41,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A41,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>NO CORTAR hasta confirmar el riel HRE126-55 y la bandeja.</v>
+        <v>NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7697,7 +7707,7 @@
       </c>
       <c r="N44" s="43" t="str">
         <f>IF(LEN(TRIM(IF($L44="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L42,2)&amp;" × "&amp;ROUND(Despiece!M42,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A42,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L44="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L42,2)&amp;" × "&amp;ROUND(Despiece!M42,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A42,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>Si no la cantean: cortar a 549,1 × 59,1 y cantear en el armado. NO CORTAR hasta confirmar el riel HRE126-55 y la bandeja.</v>
+        <v>Si no la cantean: cortar a 549,1 × 59,1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7755,7 +7765,7 @@
       </c>
       <c r="N45" s="43" t="str">
         <f>IF(LEN(TRIM(IF($L45="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L43,2)&amp;" × "&amp;ROUND(Despiece!M43,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A43,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L45="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!L43,2)&amp;" × "&amp;ROUND(Despiece!M43,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A43,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>Si no la cantean: cortar a 312,1 × 59,1 y cantear en el armado. NO CORTAR hasta confirmar el riel HRE126-55 y la bandeja.</v>
+        <v>Si no la cantean: cortar a 312,1 × 59,1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -9790,20 +9800,20 @@
     </row>
     <row r="82" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C82" s="34" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D82" s="35"/>
       <c r="E82" s="35"/>
       <c r="F82" s="34" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C83" s="34" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D83" s="35"/>
       <c r="E83" s="35"/>
@@ -9818,7 +9828,7 @@
     </row>
     <row r="84" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C84" s="34" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D84" s="35"/>
       <c r="E84" s="35"/>
@@ -9833,7 +9843,7 @@
     </row>
     <row r="85" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C85" s="34" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D85" s="35"/>
       <c r="E85" s="35"/>
@@ -9848,20 +9858,20 @@
     </row>
     <row r="87" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C87" s="34" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D87" s="35"/>
       <c r="E87" s="35"/>
       <c r="F87" s="34" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G87" s="34" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C88" s="28" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F88" s="32">
         <f>SUMPRODUCT(Despiece!$G$5:$G$78,(Despiece!$H$5:$H$78="2")+(Despiece!$I$5:$I$78="2")+(Despiece!$J$5:$J$78="2")+(Despiece!$K$5:$K$78="2"),--($L$7:$L$80="Pequeña"))</f>
@@ -9874,7 +9884,7 @@
     </row>
     <row r="89" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C89" s="28" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F89" s="2">
         <f>G83</f>
@@ -9887,7 +9897,7 @@
     </row>
     <row r="90" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C90" s="28" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F90" s="37">
         <v>0.1</v>
@@ -9898,7 +9908,7 @@
     </row>
     <row r="91" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C91" s="28" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F91" s="38">
         <v>0.2</v>
@@ -9909,7 +9919,7 @@
     </row>
     <row r="92" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C92" s="34" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D92" s="35"/>
       <c r="E92" s="35"/>
@@ -9924,7 +9934,7 @@
     </row>
     <row r="93" spans="3:14" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="56" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D93" s="53"/>
       <c r="E93" s="53"/>
@@ -9940,14 +9950,14 @@
     </row>
     <row r="94" spans="3:14" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F94" s="46"/>
       <c r="G94" s="46"/>
     </row>
     <row r="95" spans="3:14" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F95" s="46">
         <v>0</v>
@@ -9958,7 +9968,7 @@
     </row>
     <row r="96" spans="3:14" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="47" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D96" s="47"/>
       <c r="E96" s="47"/>
@@ -9973,7 +9983,7 @@
     </row>
     <row r="97" spans="3:14" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="57" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D97" s="53"/>
       <c r="E97" s="53"/>
@@ -10014,30 +10024,30 @@
   <sheetData>
     <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C2" s="19">
         <v>4</v>
@@ -10050,15 +10060,15 @@
         <v>1463488</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C3" s="19">
         <v>1</v>
@@ -10071,15 +10081,15 @@
         <v>212534</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C4" s="19">
         <f>ROUNDUP(Cantos!F4/Cantos!H4,0)</f>
@@ -10093,15 +10103,15 @@
         <v>531600</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="C5" s="19">
         <f>ROUNDUP(Cantos!F5/Cantos!H5,0)</f>
@@ -10115,15 +10125,15 @@
         <v>285600</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C6" s="19">
         <v>1</v>
@@ -10136,15 +10146,15 @@
         <v>41215</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -10157,15 +10167,15 @@
         <v>51014</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C8" s="19">
         <v>1</v>
@@ -10178,15 +10188,15 @@
         <v>47034</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C9" s="19">
         <v>12</v>
@@ -10199,15 +10209,15 @@
         <v>213000</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="C10" s="19">
         <v>1</v>
@@ -10220,15 +10230,15 @@
         <v>63539</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C11" s="19">
         <v>1</v>
@@ -10241,15 +10251,15 @@
         <v>38791</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C12" s="19">
         <v>24</v>
@@ -10262,57 +10272,57 @@
         <v>49008</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C13" s="19">
         <v>5</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E13" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C14" s="19">
         <v>1</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E14" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C15" s="19">
         <v>1</v>
@@ -10325,15 +10335,15 @@
         <v>122902</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C16" s="19">
         <v>1</v>
@@ -10346,15 +10356,15 @@
         <v>109700</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C17" s="19">
         <v>1</v>
@@ -10367,36 +10377,36 @@
         <v>12560</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C18" s="19">
         <v>1</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E18" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C19" s="19">
         <v>2</v>
@@ -10409,15 +10419,15 @@
         <v>18252</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C20" s="19">
         <v>10</v>
@@ -10430,15 +10440,15 @@
         <v>29980</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C21" s="19">
         <v>1</v>
@@ -10451,15 +10461,15 @@
         <v>1486300</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C22" s="19">
         <v>1</v>
@@ -10472,15 +10482,15 @@
         <v>209900</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C23" s="19">
         <v>1</v>
@@ -10493,202 +10503,202 @@
         <v>1864800</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C24" s="19">
         <v>1</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E24" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C25" s="19">
         <v>1</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E25" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C26" s="19">
         <v>1</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E26" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C27" s="19">
         <v>1</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E27" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C28" s="19">
         <v>1</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E28" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C29" s="19">
         <v>1</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E29" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C30" s="19">
         <v>1</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E30" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C31" s="19">
         <v>1</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E31" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C32" s="19">
         <v>1</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E32" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Por cotizar</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="18"/>
@@ -10701,7 +10711,7 @@
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="18"/>
@@ -10714,7 +10724,7 @@
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="18"/>
@@ -10727,7 +10737,7 @@
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -10740,7 +10750,7 @@
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -10753,7 +10763,7 @@
     <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22"/>
       <c r="B38" s="22" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -10762,13 +10772,13 @@
         <v>6851217</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -10777,13 +10787,13 @@
         <v>12</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -10792,7 +10802,7 @@
         <v>Pendiente de cotizaciones</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -10824,7 +10834,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10844,7 +10854,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I2" s="14">
         <v>0.05</v>
@@ -10852,35 +10862,35 @@
     </row>
     <row r="3" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>254</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>258</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C4" s="7">
         <f>SUMPRODUCT(Despiece!$G$5:$G$78,Despiece!$E$5:$E$78,(Despiece!$H$5:$H$78="2")+(Despiece!$I$5:$I$78="2"))/1000+SUMPRODUCT(Despiece!$G$5:$G$78,Despiece!$F$5:$F$78,(Despiece!$J$5:$J$78="2")+(Despiece!$K$5:$K$78="2"))/1000</f>
@@ -10906,10 +10916,10 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C5" s="7">
         <f>SUMPRODUCT(Despiece!$G$5:$G$78,Despiece!$E$5:$E$78,(Despiece!$H$5:$H$78="0.45")+(Despiece!$I$5:$I$78="0.45"))/1000+SUMPRODUCT(Despiece!$G$5:$G$78,Despiece!$F$5:$F$78,(Despiece!$J$5:$J$78="0.45")+(Despiece!$K$5:$K$78="0.45"))/1000</f>
@@ -10946,7 +10956,7 @@
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B7" s="53"/>
       <c r="C7" s="53"/>
@@ -10978,12 +10988,12 @@
   <sheetData>
     <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -10991,16 +11001,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -11008,16 +11018,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -11025,16 +11035,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -11042,16 +11052,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -11059,16 +11069,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -11076,16 +11086,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -11093,16 +11103,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -11110,16 +11120,16 @@
         <v>7</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -11127,16 +11137,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -11144,16 +11154,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -11161,16 +11171,16 @@
         <v>10</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -11178,16 +11188,16 @@
         <v>11</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -11197,7 +11207,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C35FAE-E2A1-4C9F-A08B-6BCDCAA7F1FA}">
-  <dimension ref="A2:D15"/>
+  <dimension ref="A2:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.77734375" customWidth="1"/>
@@ -11208,152 +11218,166 @@
   <sheetData>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="49" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="51" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="51" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="51" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="51" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="51" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="51" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="51" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="51" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>411</v>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -11385,7 +11409,7 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -11397,7 +11421,7 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B3" s="24">
         <v>3000</v>
@@ -11411,7 +11435,7 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B4" s="24">
         <v>2600</v>
@@ -11425,7 +11449,7 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B5" s="24">
         <v>200</v>
@@ -11439,7 +11463,7 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B6" s="5">
         <f>B3-B5-B4</f>
@@ -11454,7 +11478,7 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B7" s="5">
         <f>B3-B5</f>
@@ -11469,7 +11493,7 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B8" s="24">
         <v>15</v>
@@ -11503,33 +11527,33 @@
     </row>
     <row r="11" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="F11" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="G11" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="H11" s="17" t="s">
         <v>305</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B12" s="10">
         <f>B6</f>
@@ -11550,15 +11574,15 @@
         <v>620</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B13" s="10">
         <f>B6+B8</f>
@@ -11580,10 +11604,10 @@
         <v>595</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11611,10 +11635,10 @@
         <v>580</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11642,10 +11666,10 @@
         <v>580</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11673,10 +11697,10 @@
         <v>580</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11704,10 +11728,10 @@
         <v>580</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11735,10 +11759,10 @@
         <v>580</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11766,10 +11790,10 @@
         <v>320</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11797,10 +11821,10 @@
         <v>320</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11828,10 +11852,10 @@
         <v>320</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11859,10 +11883,10 @@
         <v>320</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11890,10 +11914,10 @@
         <v>320</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -11908,7 +11932,7 @@
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B25" s="10">
         <f>SUM(D14:D18)</f>
@@ -11923,7 +11947,7 @@
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B26" s="10">
         <f>D13+(B13-B6)+(B7-C18)</f>
@@ -11938,7 +11962,7 @@
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B27" s="10">
         <f>B25+B26</f>
@@ -11953,7 +11977,7 @@
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B28" s="10">
         <f>SUMIF(Despiece!D5:D78,"Melamina Cartagena RH 15",Despiece!G5:G78)</f>
@@ -11968,7 +11992,7 @@
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B29" s="5">
         <f>SUMIF(Despiece!D5:D78,"Fondo melamina 6",Despiece!G5:G78)</f>
@@ -11983,7 +12007,7 @@
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
